--- a/output/pdf_financials_xlsx/HAM.xlsx
+++ b/output/pdf_financials_xlsx/HAM.xlsx
@@ -3046,13 +3046,13 @@
         <v>2.929</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.062</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.062</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.062</v>
       </c>
     </row>
     <row r="93">
@@ -3741,25 +3741,25 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>-7.858701</v>
+        <v>-7.855701</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>-8.182691999999999</v>
+        <v>-7.764063</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>-0.216</v>
+        <v>0.498</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.398</v>
+        <v>-0.213</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>-1.297</v>
+        <v>-1.082</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>-12.499</v>
+        <v>-12.344</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>-4.204</v>
+        <v>-4.117</v>
       </c>
     </row>
     <row r="119">
@@ -5468,7 +5468,11 @@
           <t>Warrant reserve 15</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -6972,7 +6976,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -8757,7 +8765,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -12031,7 +12043,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -13047,7 +13063,11 @@
           <t>Exploration and evaluation expenditures 10</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E176" s="5" t="n">
         <v>0.003</v>
       </c>

--- a/output/pdf_financials_xlsx/HAM.xlsx
+++ b/output/pdf_financials_xlsx/HAM.xlsx
@@ -673,25 +673,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>29.739054</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>34.704768</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>10.186</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>6.06</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>23.584</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>60.92</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>61.943</v>
       </c>
     </row>
     <row r="11">
@@ -741,13 +741,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.044</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.073</v>
       </c>
     </row>
     <row r="13">
@@ -1231,13 +1231,13 @@
         <v>2.957</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>49.457</v>
+        <v>49.501</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>36.543</v>
+        <v>36.633</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>30.409</v>
+        <v>30.482</v>
       </c>
     </row>
     <row r="28">
@@ -1287,13 +1287,13 @@
         <v>2.957</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>49.457</v>
+        <v>49.501</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>36.543</v>
+        <v>36.633</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>30.409</v>
+        <v>30.482</v>
       </c>
     </row>
     <row r="30">
@@ -1315,13 +1315,13 @@
         <v>44.2532175995211</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>140.132604199133</v>
+        <v>140.2572748137024</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>32.75460265672338</v>
+        <v>32.83527239481563</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>36.66517959414978</v>
+        <v>36.75319821069004</v>
       </c>
     </row>
     <row r="31">
@@ -1403,10 +1403,10 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.289</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.289</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -1795,10 +1795,10 @@
         <v>2.57</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.82</v>
+        <v>2.814</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>29.499</v>
+        <v>27.21</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>33.397</v>
@@ -4649,7 +4649,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -5997,7 +6001,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6101,7 +6105,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -7182,7 +7190,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -7231,7 +7243,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -7896,7 +7912,11 @@
           <t>Reclamation deposits 9</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E73" s="5" t="n">
         <v>0.1413</v>
       </c>
@@ -15188,7 +15208,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E219" s="5" t="n">
@@ -16370,7 +16390,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -18993,7 +19013,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">

--- a/output/pdf_financials_xlsx/HAM.xlsx
+++ b/output/pdf_financials_xlsx/HAM.xlsx
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.154991</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -3582,10 +3582,10 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>2.468</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.183</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -5282,7 +5282,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -6782,7 +6786,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -8383,7 +8391,11 @@
           <t>Lease liabilities 12</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -8924,7 +8936,11 @@
           <t>Deferred tax expense 13</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -10433,7 +10449,11 @@
           <t>Proceeds on dispositions to property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -10841,7 +10861,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -11653,7 +11677,11 @@
           <t>Proceeds on dispositions of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -12265,7 +12293,11 @@
           <t>Deferred tax expense (recovery) 12(b)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -12724,7 +12756,11 @@
           <t>Proceeds on dispositions of property, plant and equipment 7(b)</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -13236,7 +13272,11 @@
           <t>Deferred tax expense (recovery) 15(b)</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E179" s="5" t="n">
         <v>0.475</v>
       </c>
@@ -14260,7 +14300,11 @@
           <t>Proceeds on dispositions of property, plant and equipment 6(h)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E199" s="5" t="n">
         <v>0.154991</v>
       </c>
